--- a/public/templates/examples/A-041-DefaultCredentialRemediationLog-EXAMPLE-M.xlsx
+++ b/public/templates/examples/A-041-DefaultCredentialRemediationLog-EXAMPLE-M.xlsx
@@ -3,11 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Log!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -15,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -186,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -241,6 +246,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -748,11 +757,9 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
+    <row r="12" ht="34.7" customHeight="1">
+      <c r="A12" s="22">
+        <v>46034</v>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
@@ -780,11 +787,9 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
+    <row r="13" ht="34.7" customHeight="1">
+      <c r="A13" s="22">
+        <v>46050</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
@@ -812,11 +817,9 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
+    <row r="14" ht="34.7" customHeight="1">
+      <c r="A14" s="22">
+        <v>46067</v>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
@@ -966,10 +969,8 @@
           <t>/s/ Priya Nair</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
+      <c r="D29" s="23">
+        <v>46082</v>
       </c>
       <c r="E29" s="13" t="n"/>
       <c r="F29" s="13" t="n"/>
@@ -990,10 +991,8 @@
           <t>/s/ Anthony Reyes</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
+      <c r="D30" s="23">
+        <v>46082</v>
       </c>
       <c r="E30" s="13" t="n"/>
       <c r="F30" s="13" t="n"/>
@@ -1092,10 +1091,8 @@
       <c r="A46" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
+      <c r="B46" s="22">
+        <v>46082</v>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
@@ -1111,12 +1108,12 @@
       <c r="F46" s="11" t="n"/>
     </row>
     <row r="47"/>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="2" t="n"/>
+    <row r="48">
+      <c r="A48"/>
     </row>
     <row r="49"/>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="28">
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A27:F27"/>
@@ -1139,7 +1136,6 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A4:B4"/>
@@ -1148,7 +1144,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>